--- a/documents/Uchebny_klass_OT_2027/04_Smeta_rynochnye_ceny.xlsx
+++ b/documents/Uchebny_klass_OT_2027/04_Smeta_rynochnye_ceny.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Смета" sheetId="1" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName function="false" hidden="true" localSheetId="0" name="_xlnm._FilterDatabase" vbProcedure="false">Смета!$A$4:$L$47</definedName>
+    <definedName function="false" hidden="true" localSheetId="0" name="_xlnm._FilterDatabase" vbProcedure="false">Смета!$A$4:$K$47</definedName>
   </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="345" uniqueCount="161">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="344" uniqueCount="160">
   <si>
     <t xml:space="preserve">Смета оснащения учебного класса по охране труда</t>
   </si>
@@ -56,9 +56,6 @@
   </si>
   <si>
     <t xml:space="preserve">Обоснование / источник</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Цена в прежней редакции, ₽</t>
   </si>
   <si>
     <t xml:space="preserve">Статус проверки цены</t>
@@ -516,7 +513,7 @@
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="#,##0&quot; ₽&quot;;\(#,##0&quot; ₽)&quot;;\-"/>
   </numFmts>
-  <fonts count="14">
+  <fonts count="12">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -584,13 +581,6 @@
     </font>
     <font>
       <sz val="10"/>
-      <color rgb="FF595959"/>
-      <name val="Arial"/>
-      <family val="0"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
       <family val="0"/>
@@ -599,14 +589,6 @@
     <font>
       <b val="true"/>
       <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <b val="true"/>
-      <sz val="10"/>
-      <color rgb="FF595959"/>
       <name val="Arial"/>
       <family val="0"/>
       <charset val="1"/>
@@ -675,7 +657,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="14">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -720,23 +702,15 @@
       <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -749,7 +723,7 @@
     <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
     <cellStyle name="Percent" xfId="19" builtinId="5"/>
   </cellStyles>
-  <dxfs count="6">
+  <dxfs count="5">
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -785,14 +759,6 @@
       <fill>
         <patternFill patternType="solid">
           <fgColor rgb="FF0000FF"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF595959"/>
           <bgColor rgb="FF000000"/>
         </patternFill>
       </fill>
@@ -1045,7 +1011,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:L63"/>
+  <dimension ref="A1:K63"/>
   <sheetFormatPr defaultColWidth="8.55859375" defaultRowHeight="14.25" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="5"/>
@@ -1057,9 +1023,9 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="14"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="9"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="52"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="1" width="22"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="1" width="60"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="22"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="1" width="60"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="1" width="9"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1133,22 +1099,19 @@
       <c r="K4" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="L4" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="5" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="6" t="n">
         <v>5</v>
       </c>
       <c r="B5" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="C5" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="C5" s="6" t="s">
-        <v>15</v>
-      </c>
       <c r="D5" s="6" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E5" s="7" t="n">
         <v>4</v>
@@ -1161,19 +1124,16 @@
         <v>56000</v>
       </c>
       <c r="H5" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="I5" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="I5" s="6" t="s">
+      <c r="J5" s="11" t="s">
         <v>18</v>
       </c>
-      <c r="J5" s="11" t="n">
-        <v>28000</v>
-      </c>
-      <c r="K5" s="12" t="s">
+      <c r="K5" s="11" t="s">
         <v>19</v>
-      </c>
-      <c r="L5" s="12" t="s">
-        <v>20</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1181,13 +1141,13 @@
         <v>6</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E6" s="7" t="n">
         <v>3</v>
@@ -1200,19 +1160,16 @@
         <v>96000</v>
       </c>
       <c r="H6" s="10" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I6" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="J6" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="K6" s="11" t="s">
         <v>22</v>
-      </c>
-      <c r="J6" s="11" t="n">
-        <v>45000</v>
-      </c>
-      <c r="K6" s="12" t="s">
-        <v>19</v>
-      </c>
-      <c r="L6" s="12" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1220,13 +1177,13 @@
         <v>8</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E7" s="7" t="n">
         <v>2</v>
@@ -1239,19 +1196,16 @@
         <v>24000</v>
       </c>
       <c r="H7" s="10" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I7" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="J7" s="11" t="s">
         <v>25</v>
       </c>
-      <c r="J7" s="11" t="n">
-        <v>22000</v>
-      </c>
-      <c r="K7" s="12" t="s">
+      <c r="K7" s="11" t="s">
         <v>26</v>
-      </c>
-      <c r="L7" s="12" t="s">
-        <v>27</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1259,13 +1213,13 @@
         <v>10</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E8" s="7" t="n">
         <v>1</v>
@@ -1278,19 +1232,16 @@
         <v>12000</v>
       </c>
       <c r="H8" s="10" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I8" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="J8" s="11" t="s">
         <v>29</v>
       </c>
-      <c r="J8" s="11" t="n">
-        <v>20000</v>
-      </c>
-      <c r="K8" s="12" t="s">
+      <c r="K8" s="11" t="s">
         <v>30</v>
-      </c>
-      <c r="L8" s="12" t="s">
-        <v>31</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1298,13 +1249,13 @@
         <v>11</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E9" s="7" t="n">
         <v>1</v>
@@ -1317,19 +1268,16 @@
         <v>8000</v>
       </c>
       <c r="H9" s="10" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I9" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="J9" s="11" t="s">
+        <v>25</v>
+      </c>
+      <c r="K9" s="11" t="s">
         <v>33</v>
-      </c>
-      <c r="J9" s="11" t="n">
-        <v>15000</v>
-      </c>
-      <c r="K9" s="12" t="s">
-        <v>26</v>
-      </c>
-      <c r="L9" s="12" t="s">
-        <v>34</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1337,13 +1285,13 @@
         <v>12</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E10" s="7" t="n">
         <v>4</v>
@@ -1356,19 +1304,16 @@
         <v>8000</v>
       </c>
       <c r="H10" s="10" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I10" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="J10" s="11" t="s">
+        <v>25</v>
+      </c>
+      <c r="K10" s="11" t="s">
         <v>36</v>
-      </c>
-      <c r="J10" s="11" t="n">
-        <v>3500</v>
-      </c>
-      <c r="K10" s="12" t="s">
-        <v>26</v>
-      </c>
-      <c r="L10" s="12" t="s">
-        <v>37</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1376,13 +1321,13 @@
         <v>14</v>
       </c>
       <c r="B11" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="C11" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="C11" s="6" t="s">
+      <c r="D11" s="6" t="s">
         <v>39</v>
-      </c>
-      <c r="D11" s="6" t="s">
-        <v>40</v>
       </c>
       <c r="E11" s="7" t="n">
         <v>1</v>
@@ -1395,19 +1340,16 @@
         <v>220000</v>
       </c>
       <c r="H11" s="10" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I11" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="J11" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="K11" s="11" t="s">
         <v>41</v>
-      </c>
-      <c r="J11" s="11" t="n">
-        <v>220000</v>
-      </c>
-      <c r="K11" s="12" t="s">
-        <v>19</v>
-      </c>
-      <c r="L11" s="12" t="s">
-        <v>42</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1415,13 +1357,13 @@
         <v>18</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E12" s="7" t="n">
         <v>1</v>
@@ -1434,19 +1376,16 @@
         <v>17000</v>
       </c>
       <c r="H12" s="10" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I12" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="J12" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="K12" s="11" t="s">
         <v>44</v>
-      </c>
-      <c r="J12" s="11" t="n">
-        <v>30000</v>
-      </c>
-      <c r="K12" s="12" t="s">
-        <v>19</v>
-      </c>
-      <c r="L12" s="12" t="s">
-        <v>45</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1454,13 +1393,13 @@
         <v>19</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D13" s="6" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E13" s="7" t="n">
         <v>1</v>
@@ -1473,19 +1412,16 @@
         <v>8000</v>
       </c>
       <c r="H13" s="10" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I13" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="J13" s="11" t="s">
+        <v>25</v>
+      </c>
+      <c r="K13" s="11" t="s">
         <v>47</v>
-      </c>
-      <c r="J13" s="11" t="n">
-        <v>15000</v>
-      </c>
-      <c r="K13" s="12" t="s">
-        <v>26</v>
-      </c>
-      <c r="L13" s="12" t="s">
-        <v>48</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1493,13 +1429,13 @@
         <v>21</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D14" s="6" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E14" s="7" t="n">
         <v>1</v>
@@ -1512,19 +1448,16 @@
         <v>80000</v>
       </c>
       <c r="H14" s="10" t="s">
+        <v>49</v>
+      </c>
+      <c r="I14" s="6" t="s">
         <v>50</v>
       </c>
-      <c r="I14" s="6" t="s">
+      <c r="J14" s="11" t="s">
+        <v>29</v>
+      </c>
+      <c r="K14" s="11" t="s">
         <v>51</v>
-      </c>
-      <c r="J14" s="11" t="n">
-        <v>120000</v>
-      </c>
-      <c r="K14" s="12" t="s">
-        <v>30</v>
-      </c>
-      <c r="L14" s="12" t="s">
-        <v>52</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1532,13 +1465,13 @@
         <v>31</v>
       </c>
       <c r="B15" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="C15" s="6" t="s">
         <v>53</v>
       </c>
-      <c r="C15" s="6" t="s">
-        <v>54</v>
-      </c>
       <c r="D15" s="6" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E15" s="7" t="n">
         <v>1</v>
@@ -1551,19 +1484,16 @@
         <v>90000</v>
       </c>
       <c r="H15" s="10" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I15" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="J15" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="K15" s="11" t="s">
         <v>55</v>
-      </c>
-      <c r="J15" s="11" t="n">
-        <v>320000</v>
-      </c>
-      <c r="K15" s="12" t="s">
-        <v>19</v>
-      </c>
-      <c r="L15" s="12" t="s">
-        <v>56</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1571,13 +1501,13 @@
         <v>32</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C16" s="6" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D16" s="6" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E16" s="7" t="n">
         <v>2</v>
@@ -1590,19 +1520,16 @@
         <v>110000</v>
       </c>
       <c r="H16" s="10" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I16" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="J16" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="K16" s="11" t="s">
         <v>58</v>
-      </c>
-      <c r="J16" s="11" t="n">
-        <v>75000</v>
-      </c>
-      <c r="K16" s="12" t="s">
-        <v>19</v>
-      </c>
-      <c r="L16" s="12" t="s">
-        <v>59</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1610,13 +1537,13 @@
         <v>33</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C17" s="6" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D17" s="6" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E17" s="7" t="n">
         <v>1</v>
@@ -1629,19 +1556,16 @@
         <v>19000</v>
       </c>
       <c r="H17" s="10" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I17" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="J17" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="K17" s="11" t="s">
         <v>61</v>
-      </c>
-      <c r="J17" s="11" t="n">
-        <v>60000</v>
-      </c>
-      <c r="K17" s="12" t="s">
-        <v>19</v>
-      </c>
-      <c r="L17" s="12" t="s">
-        <v>62</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1649,13 +1573,13 @@
         <v>34</v>
       </c>
       <c r="B18" s="6" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C18" s="6" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D18" s="6" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E18" s="7" t="n">
         <v>1</v>
@@ -1668,19 +1592,16 @@
         <v>45000</v>
       </c>
       <c r="H18" s="10" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I18" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="J18" s="11" t="s">
+        <v>25</v>
+      </c>
+      <c r="K18" s="11" t="s">
         <v>64</v>
-      </c>
-      <c r="J18" s="11" t="n">
-        <v>45000</v>
-      </c>
-      <c r="K18" s="12" t="s">
-        <v>26</v>
-      </c>
-      <c r="L18" s="12" t="s">
-        <v>65</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1688,13 +1609,13 @@
         <v>35</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C19" s="6" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D19" s="6" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E19" s="7" t="n">
         <v>1</v>
@@ -1707,19 +1628,16 @@
         <v>10000</v>
       </c>
       <c r="H19" s="10" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I19" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="J19" s="11" t="s">
+        <v>29</v>
+      </c>
+      <c r="K19" s="11" t="s">
         <v>67</v>
-      </c>
-      <c r="J19" s="11" t="n">
-        <v>35000</v>
-      </c>
-      <c r="K19" s="12" t="s">
-        <v>30</v>
-      </c>
-      <c r="L19" s="12" t="s">
-        <v>68</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1727,13 +1645,13 @@
         <v>36</v>
       </c>
       <c r="B20" s="6" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C20" s="6" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D20" s="6" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E20" s="7" t="n">
         <v>2</v>
@@ -1746,19 +1664,16 @@
         <v>10000</v>
       </c>
       <c r="H20" s="10" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I20" s="6" t="s">
-        <v>67</v>
-      </c>
-      <c r="J20" s="11" t="n">
-        <v>8000</v>
-      </c>
-      <c r="K20" s="12" t="s">
-        <v>19</v>
-      </c>
-      <c r="L20" s="12" t="s">
-        <v>70</v>
+        <v>66</v>
+      </c>
+      <c r="J20" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="K20" s="11" t="s">
+        <v>69</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1766,13 +1681,13 @@
         <v>37</v>
       </c>
       <c r="B21" s="6" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C21" s="6" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D21" s="6" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E21" s="7" t="n">
         <v>1</v>
@@ -1785,19 +1700,16 @@
         <v>30000</v>
       </c>
       <c r="H21" s="10" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I21" s="6" t="s">
-        <v>67</v>
-      </c>
-      <c r="J21" s="11" t="n">
-        <v>35000</v>
-      </c>
-      <c r="K21" s="12" t="s">
-        <v>19</v>
-      </c>
-      <c r="L21" s="12" t="s">
-        <v>72</v>
+        <v>66</v>
+      </c>
+      <c r="J21" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="K21" s="11" t="s">
+        <v>71</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1805,13 +1717,13 @@
         <v>38</v>
       </c>
       <c r="B22" s="6" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C22" s="6" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D22" s="6" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E22" s="7" t="n">
         <v>3</v>
@@ -1824,19 +1736,16 @@
         <v>4500</v>
       </c>
       <c r="H22" s="10" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I22" s="6" t="s">
+        <v>73</v>
+      </c>
+      <c r="J22" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="K22" s="11" t="s">
         <v>74</v>
-      </c>
-      <c r="J22" s="11" t="n">
-        <v>3500</v>
-      </c>
-      <c r="K22" s="12" t="s">
-        <v>19</v>
-      </c>
-      <c r="L22" s="12" t="s">
-        <v>75</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1844,13 +1753,13 @@
         <v>39</v>
       </c>
       <c r="B23" s="6" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C23" s="6" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D23" s="6" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E23" s="7" t="n">
         <v>1</v>
@@ -1863,19 +1772,16 @@
         <v>30000</v>
       </c>
       <c r="H23" s="10" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I23" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="J23" s="11" t="s">
+        <v>25</v>
+      </c>
+      <c r="K23" s="11" t="s">
         <v>77</v>
-      </c>
-      <c r="J23" s="11" t="n">
-        <v>60000</v>
-      </c>
-      <c r="K23" s="12" t="s">
-        <v>26</v>
-      </c>
-      <c r="L23" s="12" t="s">
-        <v>78</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1883,13 +1789,13 @@
         <v>40</v>
       </c>
       <c r="B24" s="6" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C24" s="6" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D24" s="6" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E24" s="7" t="n">
         <v>1</v>
@@ -1902,19 +1808,16 @@
         <v>45000</v>
       </c>
       <c r="H24" s="10" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="I24" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="J24" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="K24" s="11" t="s">
         <v>80</v>
-      </c>
-      <c r="J24" s="11" t="n">
-        <v>65000</v>
-      </c>
-      <c r="K24" s="12" t="s">
-        <v>19</v>
-      </c>
-      <c r="L24" s="12" t="s">
-        <v>81</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1922,13 +1825,13 @@
         <v>42</v>
       </c>
       <c r="B25" s="6" t="s">
+        <v>81</v>
+      </c>
+      <c r="C25" s="6" t="s">
         <v>82</v>
       </c>
-      <c r="C25" s="6" t="s">
-        <v>83</v>
-      </c>
       <c r="D25" s="6" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E25" s="7" t="n">
         <v>2</v>
@@ -1941,19 +1844,16 @@
         <v>30000</v>
       </c>
       <c r="H25" s="10" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I25" s="6" t="s">
-        <v>67</v>
-      </c>
-      <c r="J25" s="11" t="n">
-        <v>30000</v>
-      </c>
-      <c r="K25" s="12" t="s">
-        <v>19</v>
-      </c>
-      <c r="L25" s="12" t="s">
-        <v>84</v>
+        <v>66</v>
+      </c>
+      <c r="J25" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="K25" s="11" t="s">
+        <v>83</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1961,13 +1861,13 @@
         <v>43</v>
       </c>
       <c r="B26" s="6" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C26" s="6" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D26" s="6" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E26" s="7" t="n">
         <v>1</v>
@@ -1980,19 +1880,16 @@
         <v>35000</v>
       </c>
       <c r="H26" s="10" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I26" s="6" t="s">
+        <v>85</v>
+      </c>
+      <c r="J26" s="11" t="s">
+        <v>25</v>
+      </c>
+      <c r="K26" s="11" t="s">
         <v>86</v>
-      </c>
-      <c r="J26" s="11" t="n">
-        <v>70000</v>
-      </c>
-      <c r="K26" s="12" t="s">
-        <v>26</v>
-      </c>
-      <c r="L26" s="12" t="s">
-        <v>87</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2000,13 +1897,13 @@
         <v>44</v>
       </c>
       <c r="B27" s="6" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C27" s="6" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D27" s="6" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E27" s="7" t="n">
         <v>1</v>
@@ -2019,19 +1916,16 @@
         <v>5000</v>
       </c>
       <c r="H27" s="10" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I27" s="6" t="s">
+        <v>88</v>
+      </c>
+      <c r="J27" s="11" t="s">
+        <v>25</v>
+      </c>
+      <c r="K27" s="11" t="s">
         <v>89</v>
-      </c>
-      <c r="J27" s="11" t="n">
-        <v>15000</v>
-      </c>
-      <c r="K27" s="12" t="s">
-        <v>26</v>
-      </c>
-      <c r="L27" s="12" t="s">
-        <v>90</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2039,13 +1933,13 @@
         <v>45</v>
       </c>
       <c r="B28" s="6" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C28" s="6" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D28" s="6" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E28" s="7" t="n">
         <v>1</v>
@@ -2058,19 +1952,16 @@
         <v>30000</v>
       </c>
       <c r="H28" s="10" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I28" s="6" t="s">
+        <v>91</v>
+      </c>
+      <c r="J28" s="11" t="s">
+        <v>29</v>
+      </c>
+      <c r="K28" s="11" t="s">
         <v>92</v>
-      </c>
-      <c r="J28" s="11" t="n">
-        <v>60000</v>
-      </c>
-      <c r="K28" s="12" t="s">
-        <v>30</v>
-      </c>
-      <c r="L28" s="12" t="s">
-        <v>93</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2078,13 +1969,13 @@
         <v>46</v>
       </c>
       <c r="B29" s="6" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C29" s="6" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D29" s="6" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E29" s="7" t="n">
         <v>1</v>
@@ -2097,19 +1988,16 @@
         <v>5000</v>
       </c>
       <c r="H29" s="10" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I29" s="6" t="s">
+        <v>94</v>
+      </c>
+      <c r="J29" s="11" t="s">
+        <v>25</v>
+      </c>
+      <c r="K29" s="11" t="s">
         <v>95</v>
-      </c>
-      <c r="J29" s="11" t="n">
-        <v>15000</v>
-      </c>
-      <c r="K29" s="12" t="s">
-        <v>26</v>
-      </c>
-      <c r="L29" s="12" t="s">
-        <v>96</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2117,13 +2005,13 @@
         <v>47</v>
       </c>
       <c r="B30" s="6" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C30" s="6" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D30" s="6" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E30" s="7" t="n">
         <v>1</v>
@@ -2136,19 +2024,16 @@
         <v>5000</v>
       </c>
       <c r="H30" s="10" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I30" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="J30" s="11" t="s">
+        <v>25</v>
+      </c>
+      <c r="K30" s="11" t="s">
         <v>98</v>
-      </c>
-      <c r="J30" s="11" t="n">
-        <v>10000</v>
-      </c>
-      <c r="K30" s="12" t="s">
-        <v>26</v>
-      </c>
-      <c r="L30" s="12" t="s">
-        <v>99</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2156,13 +2041,13 @@
         <v>48</v>
       </c>
       <c r="B31" s="6" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C31" s="6" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D31" s="6" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E31" s="7" t="n">
         <v>1</v>
@@ -2175,19 +2060,16 @@
         <v>8000</v>
       </c>
       <c r="H31" s="10" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I31" s="6" t="s">
+        <v>100</v>
+      </c>
+      <c r="J31" s="11" t="s">
+        <v>25</v>
+      </c>
+      <c r="K31" s="11" t="s">
         <v>101</v>
-      </c>
-      <c r="J31" s="11" t="n">
-        <v>20000</v>
-      </c>
-      <c r="K31" s="12" t="s">
-        <v>26</v>
-      </c>
-      <c r="L31" s="12" t="s">
-        <v>102</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2195,13 +2077,13 @@
         <v>49</v>
       </c>
       <c r="B32" s="6" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C32" s="6" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D32" s="6" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E32" s="7" t="n">
         <v>1</v>
@@ -2214,19 +2096,16 @@
         <v>6000</v>
       </c>
       <c r="H32" s="10" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I32" s="6" t="s">
-        <v>67</v>
-      </c>
-      <c r="J32" s="11" t="n">
-        <v>10000</v>
-      </c>
-      <c r="K32" s="12" t="s">
-        <v>26</v>
-      </c>
-      <c r="L32" s="12" t="s">
-        <v>104</v>
+        <v>66</v>
+      </c>
+      <c r="J32" s="11" t="s">
+        <v>25</v>
+      </c>
+      <c r="K32" s="11" t="s">
+        <v>103</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2234,13 +2113,13 @@
         <v>50</v>
       </c>
       <c r="B33" s="6" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C33" s="6" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D33" s="6" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E33" s="7" t="n">
         <v>1</v>
@@ -2253,19 +2132,16 @@
         <v>6000</v>
       </c>
       <c r="H33" s="10" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I33" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="J33" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="K33" s="11" t="s">
         <v>106</v>
-      </c>
-      <c r="J33" s="11" t="n">
-        <v>25000</v>
-      </c>
-      <c r="K33" s="12" t="s">
-        <v>19</v>
-      </c>
-      <c r="L33" s="12" t="s">
-        <v>107</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2273,13 +2149,13 @@
         <v>51</v>
       </c>
       <c r="B34" s="6" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C34" s="6" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D34" s="6" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E34" s="7" t="n">
         <v>1</v>
@@ -2292,19 +2168,16 @@
         <v>10000</v>
       </c>
       <c r="H34" s="10" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I34" s="6" t="s">
-        <v>67</v>
-      </c>
-      <c r="J34" s="11" t="n">
-        <v>15000</v>
-      </c>
-      <c r="K34" s="12" t="s">
-        <v>26</v>
-      </c>
-      <c r="L34" s="12" t="s">
-        <v>109</v>
+        <v>66</v>
+      </c>
+      <c r="J34" s="11" t="s">
+        <v>25</v>
+      </c>
+      <c r="K34" s="11" t="s">
+        <v>108</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2312,13 +2185,13 @@
         <v>52</v>
       </c>
       <c r="B35" s="6" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C35" s="6" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D35" s="6" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E35" s="7" t="n">
         <v>1</v>
@@ -2331,19 +2204,16 @@
         <v>120000</v>
       </c>
       <c r="H35" s="10" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="I35" s="6" t="s">
+        <v>110</v>
+      </c>
+      <c r="J35" s="11" t="s">
+        <v>29</v>
+      </c>
+      <c r="K35" s="11" t="s">
         <v>111</v>
-      </c>
-      <c r="J35" s="11" t="n">
-        <v>120000</v>
-      </c>
-      <c r="K35" s="12" t="s">
-        <v>30</v>
-      </c>
-      <c r="L35" s="12" t="s">
-        <v>112</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="39" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2351,13 +2221,13 @@
         <v>53</v>
       </c>
       <c r="B36" s="6" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C36" s="6" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="D36" s="6" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E36" s="7" t="n">
         <v>2</v>
@@ -2370,19 +2240,16 @@
         <v>70000</v>
       </c>
       <c r="H36" s="10" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I36" s="6" t="s">
+        <v>113</v>
+      </c>
+      <c r="J36" s="11" t="s">
+        <v>29</v>
+      </c>
+      <c r="K36" s="11" t="s">
         <v>114</v>
-      </c>
-      <c r="J36" s="11" t="n">
-        <v>60000</v>
-      </c>
-      <c r="K36" s="12" t="s">
-        <v>30</v>
-      </c>
-      <c r="L36" s="12" t="s">
-        <v>115</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2390,13 +2257,13 @@
         <v>55</v>
       </c>
       <c r="B37" s="6" t="s">
+        <v>115</v>
+      </c>
+      <c r="C37" s="6" t="s">
         <v>116</v>
       </c>
-      <c r="C37" s="6" t="s">
-        <v>117</v>
-      </c>
       <c r="D37" s="6" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E37" s="7" t="n">
         <v>2</v>
@@ -2409,19 +2276,16 @@
         <v>12000</v>
       </c>
       <c r="H37" s="10" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I37" s="6" t="s">
-        <v>67</v>
-      </c>
-      <c r="J37" s="11" t="n">
-        <v>6000</v>
-      </c>
-      <c r="K37" s="12" t="s">
-        <v>26</v>
-      </c>
-      <c r="L37" s="12" t="s">
-        <v>118</v>
+        <v>66</v>
+      </c>
+      <c r="J37" s="11" t="s">
+        <v>25</v>
+      </c>
+      <c r="K37" s="11" t="s">
+        <v>117</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2429,13 +2293,13 @@
         <v>56</v>
       </c>
       <c r="B38" s="6" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C38" s="6" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D38" s="6" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E38" s="7" t="n">
         <v>1</v>
@@ -2448,19 +2312,16 @@
         <v>20000</v>
       </c>
       <c r="H38" s="10" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I38" s="6" t="s">
-        <v>67</v>
-      </c>
-      <c r="J38" s="11" t="n">
-        <v>30000</v>
-      </c>
-      <c r="K38" s="12" t="s">
-        <v>26</v>
-      </c>
-      <c r="L38" s="12" t="s">
-        <v>120</v>
+        <v>66</v>
+      </c>
+      <c r="J38" s="11" t="s">
+        <v>25</v>
+      </c>
+      <c r="K38" s="11" t="s">
+        <v>119</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2468,13 +2329,13 @@
         <v>57</v>
       </c>
       <c r="B39" s="6" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C39" s="6" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D39" s="6" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E39" s="7" t="n">
         <v>8</v>
@@ -2487,19 +2348,16 @@
         <v>80000</v>
       </c>
       <c r="H39" s="10" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I39" s="6" t="s">
+        <v>121</v>
+      </c>
+      <c r="J39" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="K39" s="11" t="s">
         <v>122</v>
-      </c>
-      <c r="J39" s="11" t="n">
-        <v>22000</v>
-      </c>
-      <c r="K39" s="12" t="s">
-        <v>19</v>
-      </c>
-      <c r="L39" s="12" t="s">
-        <v>123</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2507,13 +2365,13 @@
         <v>58</v>
       </c>
       <c r="B40" s="6" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C40" s="6" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="D40" s="6" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E40" s="7" t="n">
         <v>1</v>
@@ -2526,19 +2384,16 @@
         <v>15000</v>
       </c>
       <c r="H40" s="10" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I40" s="6" t="s">
+        <v>124</v>
+      </c>
+      <c r="J40" s="11" t="s">
+        <v>29</v>
+      </c>
+      <c r="K40" s="11" t="s">
         <v>125</v>
-      </c>
-      <c r="J40" s="11" t="n">
-        <v>35000</v>
-      </c>
-      <c r="K40" s="12" t="s">
-        <v>30</v>
-      </c>
-      <c r="L40" s="12" t="s">
-        <v>126</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2546,13 +2401,13 @@
         <v>61</v>
       </c>
       <c r="B41" s="6" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C41" s="6" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="D41" s="6" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E41" s="7" t="n">
         <v>1</v>
@@ -2565,19 +2420,16 @@
         <v>30000</v>
       </c>
       <c r="H41" s="10" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I41" s="6" t="s">
+        <v>127</v>
+      </c>
+      <c r="J41" s="11" t="s">
+        <v>29</v>
+      </c>
+      <c r="K41" s="11" t="s">
         <v>128</v>
-      </c>
-      <c r="J41" s="11" t="n">
-        <v>30000</v>
-      </c>
-      <c r="K41" s="12" t="s">
-        <v>30</v>
-      </c>
-      <c r="L41" s="12" t="s">
-        <v>129</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2585,13 +2437,13 @@
         <v>64</v>
       </c>
       <c r="B42" s="6" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C42" s="6" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="D42" s="6" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E42" s="7" t="n">
         <v>6</v>
@@ -2604,19 +2456,16 @@
         <v>60000</v>
       </c>
       <c r="H42" s="10" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="I42" s="6" t="s">
+        <v>130</v>
+      </c>
+      <c r="J42" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="K42" s="11" t="s">
         <v>131</v>
-      </c>
-      <c r="J42" s="11" t="n">
-        <v>35000</v>
-      </c>
-      <c r="K42" s="12" t="s">
-        <v>19</v>
-      </c>
-      <c r="L42" s="12" t="s">
-        <v>132</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2624,13 +2473,13 @@
         <v>71</v>
       </c>
       <c r="B43" s="6" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C43" s="6" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="D43" s="6" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E43" s="7" t="n">
         <v>1</v>
@@ -2643,19 +2492,16 @@
         <v>120000</v>
       </c>
       <c r="H43" s="10" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I43" s="6" t="s">
+        <v>133</v>
+      </c>
+      <c r="J43" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="K43" s="11" t="s">
         <v>134</v>
-      </c>
-      <c r="J43" s="11" t="n">
-        <v>120000</v>
-      </c>
-      <c r="K43" s="12" t="s">
-        <v>19</v>
-      </c>
-      <c r="L43" s="12" t="s">
-        <v>135</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2663,13 +2509,13 @@
         <v>72</v>
       </c>
       <c r="B44" s="6" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C44" s="6" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="D44" s="6" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E44" s="7" t="n">
         <v>20</v>
@@ -2682,19 +2528,16 @@
         <v>60000</v>
       </c>
       <c r="H44" s="10" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I44" s="6" t="s">
+        <v>136</v>
+      </c>
+      <c r="J44" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="K44" s="11" t="s">
         <v>137</v>
-      </c>
-      <c r="J44" s="11" t="n">
-        <v>5000</v>
-      </c>
-      <c r="K44" s="12" t="s">
-        <v>19</v>
-      </c>
-      <c r="L44" s="12" t="s">
-        <v>138</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2702,13 +2545,13 @@
         <v>73</v>
       </c>
       <c r="B45" s="6" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C45" s="6" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="D45" s="6" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E45" s="7" t="n">
         <v>2</v>
@@ -2721,19 +2564,16 @@
         <v>10000</v>
       </c>
       <c r="H45" s="10" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I45" s="6" t="s">
+        <v>139</v>
+      </c>
+      <c r="J45" s="11" t="s">
+        <v>25</v>
+      </c>
+      <c r="K45" s="11" t="s">
         <v>140</v>
-      </c>
-      <c r="J45" s="11" t="n">
-        <v>6000</v>
-      </c>
-      <c r="K45" s="12" t="s">
-        <v>26</v>
-      </c>
-      <c r="L45" s="12" t="s">
-        <v>141</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2741,13 +2581,13 @@
         <v>74</v>
       </c>
       <c r="B46" s="6" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C46" s="6" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="D46" s="6" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E46" s="7" t="n">
         <v>1</v>
@@ -2760,54 +2600,47 @@
         <v>80000</v>
       </c>
       <c r="H46" s="10" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I46" s="6" t="s">
+        <v>142</v>
+      </c>
+      <c r="J46" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="K46" s="11" t="s">
         <v>143</v>
-      </c>
-      <c r="J46" s="11" t="n">
-        <v>90000</v>
-      </c>
-      <c r="K46" s="12" t="s">
-        <v>19</v>
-      </c>
-      <c r="L46" s="12" t="s">
-        <v>144</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A47" s="3"/>
       <c r="B47" s="3"/>
-      <c r="C47" s="13" t="s">
-        <v>145</v>
+      <c r="C47" s="12" t="s">
+        <v>144</v>
       </c>
       <c r="D47" s="3"/>
       <c r="E47" s="3"/>
       <c r="F47" s="3"/>
-      <c r="G47" s="14" t="n">
+      <c r="G47" s="13" t="n">
         <f aca="false">SUM(G5:G46)</f>
         <v>1739500</v>
       </c>
       <c r="H47" s="3"/>
       <c r="I47" s="3"/>
-      <c r="J47" s="15" t="n">
-        <f aca="false">SUMPRODUCT(E5:E46,J5:J46)</f>
-        <v>2876500</v>
-      </c>
     </row>
     <row r="49" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C49" s="13" t="s">
-        <v>146</v>
+      <c r="C49" s="12" t="s">
+        <v>145</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="C50" s="4" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="52" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="C52" s="12" t="s">
         <v>147</v>
-      </c>
-    </row>
-    <row r="52" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C52" s="13" t="s">
-        <v>148</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2815,13 +2648,13 @@
         <v>75</v>
       </c>
       <c r="B53" s="6" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C53" s="6" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="D53" s="6" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E53" s="7" t="n">
         <v>10</v>
@@ -2834,19 +2667,16 @@
         <v>500000</v>
       </c>
       <c r="H53" s="10" t="s">
+        <v>149</v>
+      </c>
+      <c r="I53" s="6" t="s">
         <v>150</v>
       </c>
-      <c r="I53" s="6" t="s">
+      <c r="J53" s="11" t="s">
+        <v>29</v>
+      </c>
+      <c r="K53" s="11" t="s">
         <v>151</v>
-      </c>
-      <c r="J53" s="11" t="n">
-        <v>65000</v>
-      </c>
-      <c r="K53" s="12" t="s">
-        <v>30</v>
-      </c>
-      <c r="L53" s="12" t="s">
-        <v>152</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2854,13 +2684,13 @@
         <v>76</v>
       </c>
       <c r="B54" s="6" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C54" s="6" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D54" s="6" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E54" s="7" t="n">
         <v>1</v>
@@ -2873,33 +2703,30 @@
         <v>60000</v>
       </c>
       <c r="H54" s="10" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="I54" s="6" t="s">
+        <v>153</v>
+      </c>
+      <c r="J54" s="11" t="s">
+        <v>25</v>
+      </c>
+      <c r="K54" s="11" t="s">
         <v>154</v>
       </c>
-      <c r="J54" s="11" t="n">
-        <v>60000</v>
-      </c>
-      <c r="K54" s="12" t="s">
-        <v>26</v>
-      </c>
-      <c r="L54" s="12" t="s">
+    </row>
+    <row r="55" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="C55" s="12" t="s">
         <v>155</v>
       </c>
-    </row>
-    <row r="55" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C55" s="13" t="s">
-        <v>156</v>
-      </c>
-      <c r="G55" s="14" t="n">
+      <c r="G55" s="13" t="n">
         <f aca="false">SUM(G53:G54)</f>
         <v>560000</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C57" s="13" t="s">
-        <v>157</v>
+      <c r="C57" s="12" t="s">
+        <v>156</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2907,13 +2734,13 @@
         <v>77</v>
       </c>
       <c r="B58" s="6" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C58" s="6" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="D58" s="6" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E58" s="7" t="n">
         <v>20</v>
@@ -2926,19 +2753,16 @@
         <v>1000000</v>
       </c>
       <c r="H58" s="10" t="s">
+        <v>149</v>
+      </c>
+      <c r="I58" s="6" t="s">
         <v>150</v>
       </c>
-      <c r="I58" s="6" t="s">
+      <c r="J58" s="11" t="s">
+        <v>29</v>
+      </c>
+      <c r="K58" s="11" t="s">
         <v>151</v>
-      </c>
-      <c r="J58" s="11" t="n">
-        <v>65000</v>
-      </c>
-      <c r="K58" s="12" t="s">
-        <v>30</v>
-      </c>
-      <c r="L58" s="12" t="s">
-        <v>152</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2946,13 +2770,13 @@
         <v>78</v>
       </c>
       <c r="B59" s="6" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C59" s="6" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="D59" s="6" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E59" s="7" t="n">
         <v>1</v>
@@ -2965,50 +2789,47 @@
         <v>100000</v>
       </c>
       <c r="H59" s="10" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="I59" s="6" t="s">
+        <v>153</v>
+      </c>
+      <c r="J59" s="11" t="s">
+        <v>25</v>
+      </c>
+      <c r="K59" s="11" t="s">
         <v>154</v>
       </c>
-      <c r="J59" s="11" t="n">
-        <v>100000</v>
-      </c>
-      <c r="K59" s="12" t="s">
-        <v>26</v>
-      </c>
-      <c r="L59" s="12" t="s">
+    </row>
+    <row r="60" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="C60" s="12" t="s">
         <v>155</v>
       </c>
-    </row>
-    <row r="60" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C60" s="13" t="s">
-        <v>156</v>
-      </c>
-      <c r="G60" s="14" t="n">
+      <c r="G60" s="13" t="n">
         <f aca="false">SUM(G58:G59)</f>
         <v>1100000</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C62" s="13" t="s">
-        <v>159</v>
-      </c>
-      <c r="G62" s="14" t="n">
+      <c r="C62" s="12" t="s">
+        <v>158</v>
+      </c>
+      <c r="G62" s="13" t="n">
         <f aca="false">G47+G55</f>
         <v>2299500</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C63" s="13" t="s">
-        <v>160</v>
-      </c>
-      <c r="G63" s="14" t="n">
+      <c r="C63" s="12" t="s">
+        <v>159</v>
+      </c>
+      <c r="G63" s="13" t="n">
         <f aca="false">G47+G60</f>
         <v>2839500</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:L47"/>
+  <autoFilter ref="A4:K47"/>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
